--- a/calc_draft.xlsx
+++ b/calc_draft.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasus\Desktop\pythonapps\calculator_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDFCEA0-D94C-4F96-8F6D-92051EACD55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D921D184-F68B-4CF7-954D-C938A3646607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="44">
   <si>
     <t>Country of discharge</t>
   </si>
@@ -39,18 +39,6 @@
     <t>POL</t>
   </si>
   <si>
-    <t>railway 20DC</t>
-  </si>
-  <si>
-    <t>railway 40HQ</t>
-  </si>
-  <si>
-    <t>DTHC</t>
-  </si>
-  <si>
-    <t>sevice</t>
-  </si>
-  <si>
     <t>shipping line</t>
   </si>
   <si>
@@ -108,16 +96,70 @@
     <t>qingdao</t>
   </si>
   <si>
-    <t>Price-20'DC</t>
-  </si>
-  <si>
-    <t>Price-40'HQ</t>
-  </si>
-  <si>
     <t>20dc</t>
   </si>
   <si>
     <t>40hq</t>
+  </si>
+  <si>
+    <t>container</t>
+  </si>
+  <si>
+    <t>railway</t>
+  </si>
+  <si>
+    <t>unloading</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
+    <t>2200$</t>
+  </si>
+  <si>
+    <t>2400$</t>
+  </si>
+  <si>
+    <t>2300$</t>
+  </si>
+  <si>
+    <t>2500$</t>
+  </si>
+  <si>
+    <t>2650$</t>
+  </si>
+  <si>
+    <t>2750$</t>
+  </si>
+  <si>
+    <t>2150$</t>
+  </si>
+  <si>
+    <t>2450$</t>
+  </si>
+  <si>
+    <t>4200$</t>
+  </si>
+  <si>
+    <t>4400$</t>
+  </si>
+  <si>
+    <t>4100$</t>
+  </si>
+  <si>
+    <t>4550$</t>
+  </si>
+  <si>
+    <t>4650$</t>
+  </si>
+  <si>
+    <t>4250$</t>
+  </si>
+  <si>
+    <t>4420$</t>
+  </si>
+  <si>
+    <t>service</t>
   </si>
 </sst>
 </file>
@@ -147,7 +189,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -170,26 +212,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -470,23 +500,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="4" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.140625" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="13.7109375" customWidth="1"/>
     <col min="13" max="13" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,366 +528,541 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="J10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2">
-        <v>2000</v>
-      </c>
-      <c r="M2" s="2">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="J13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2">
-        <v>2200</v>
-      </c>
-      <c r="M3" s="2">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2">
-        <v>2350</v>
-      </c>
-      <c r="M4" s="2">
-        <v>4250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2">
-        <v>2150</v>
-      </c>
-      <c r="M5" s="2">
-        <v>4150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2450</v>
-      </c>
-      <c r="M6" s="2">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2">
-        <v>2500</v>
-      </c>
-      <c r="M7" s="2">
-        <v>5800</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2">
-        <v>2100</v>
-      </c>
-      <c r="M8" s="2">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2">
-        <v>2100</v>
-      </c>
-      <c r="M9" s="2">
-        <v>5400</v>
+      <c r="J17" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/calc_draft.xlsx
+++ b/calc_draft.xlsx
@@ -8,27 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasus\Desktop\pythonapps\calculator_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D921D184-F68B-4CF7-954D-C938A3646607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9A7A19-D3D5-43D3-9EA5-716529724A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3285" windowWidth="23325" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$L$17</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="25">
   <si>
     <t>Country of discharge</t>
   </si>
@@ -54,18 +63,6 @@
     <t>PPK-1</t>
   </si>
   <si>
-    <t>210000rub</t>
-  </si>
-  <si>
-    <t>355000rub</t>
-  </si>
-  <si>
-    <t>22000rub</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
     <t>neco</t>
   </si>
   <si>
@@ -75,15 +72,6 @@
     <t>VMTP</t>
   </si>
   <si>
-    <t>190000rub</t>
-  </si>
-  <si>
-    <t>420000rub</t>
-  </si>
-  <si>
-    <t>13500rub</t>
-  </si>
-  <si>
     <t>fesco</t>
   </si>
   <si>
@@ -105,61 +93,25 @@
     <t>container</t>
   </si>
   <si>
-    <t>railway</t>
-  </si>
-  <si>
-    <t>unloading</t>
-  </si>
-  <si>
-    <t>freight</t>
-  </si>
-  <si>
-    <t>2200$</t>
-  </si>
-  <si>
-    <t>2400$</t>
-  </si>
-  <si>
-    <t>2300$</t>
-  </si>
-  <si>
-    <t>2500$</t>
-  </si>
-  <si>
-    <t>2650$</t>
-  </si>
-  <si>
-    <t>2750$</t>
-  </si>
-  <si>
-    <t>2150$</t>
-  </si>
-  <si>
-    <t>2450$</t>
-  </si>
-  <si>
-    <t>4200$</t>
-  </si>
-  <si>
-    <t>4400$</t>
-  </si>
-  <si>
-    <t>4100$</t>
-  </si>
-  <si>
-    <t>4550$</t>
-  </si>
-  <si>
-    <t>4650$</t>
-  </si>
-  <si>
-    <t>4250$</t>
-  </si>
-  <si>
-    <t>4420$</t>
-  </si>
-  <si>
-    <t>service</t>
+    <t>validity</t>
+  </si>
+  <si>
+    <t>railway(rub)</t>
+  </si>
+  <si>
+    <t>freight(usd)</t>
+  </si>
+  <si>
+    <t>25 nov</t>
+  </si>
+  <si>
+    <t>Курс валют</t>
+  </si>
+  <si>
+    <t>unloading(rub)</t>
+  </si>
+  <si>
+    <t>total(usd)</t>
   </si>
 </sst>
 </file>
@@ -189,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -212,14 +164,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -500,24 +465,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="5" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,28 +494,31 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -560,28 +529,32 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>210000</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2200</v>
+      </c>
+      <c r="G2" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2">
+        <f>ROUND((E2 + G2) / P3 + F2, 1)</f>
+        <v>4543.3999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -589,223 +562,257 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>17</v>
+      <c r="E3" s="2">
+        <v>190000</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2400</v>
+      </c>
+      <c r="G3" s="2">
+        <v>13500</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="2">
+        <f>ROUND((E3 + G3) / P3 + F3, 1)</f>
+        <v>4455.6000000000004</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
+        <v>210000</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2300</v>
+      </c>
+      <c r="G4" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="2">
+        <f>ROUND((E4 + G4) / P3 + F4, 1)</f>
+        <v>4643.3999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
+      <c r="E5" s="2">
+        <v>190000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2500</v>
+      </c>
+      <c r="G5" s="2">
+        <v>13500</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="2">
+        <f>ROUND((E5 + G5) / P3 + F5, 1)</f>
+        <v>4555.6000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>210000</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2650</v>
+      </c>
+      <c r="G6" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="2">
+        <f>ROUND((E6 + G6) / P3 + F6, 1)</f>
+        <v>4993.3999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
+      <c r="E7" s="2">
+        <v>190000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2750</v>
+      </c>
+      <c r="G7" s="2">
+        <v>13500</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="2">
+        <f>ROUND((E7 + G7) / P3 + F7, 1)</f>
+        <v>4805.6000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2">
+        <v>210000</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2150</v>
+      </c>
+      <c r="G8" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="2">
+        <f>ROUND((E8 + G8) / P3 + F8, 1)</f>
+        <v>4493.3999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
+      <c r="E9" s="2">
+        <v>190000</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2450</v>
+      </c>
+      <c r="G9" s="2">
+        <v>13500</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="2">
+        <f>ROUND((E9 + G9) / P3 + F9, 1)</f>
+        <v>4505.6000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -816,28 +823,32 @@
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="E10" s="2">
+        <v>355000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4200</v>
+      </c>
+      <c r="G10" s="2">
+        <v>22000</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="2">
+        <f>ROUND((E10 + G10) / P3 + F10, 1)</f>
+        <v>8008.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -845,224 +856,255 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>17</v>
+      <c r="E11" s="2">
+        <v>420000</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4400</v>
+      </c>
+      <c r="G11" s="2">
+        <v>13500</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="2">
+        <f>ROUND((E11 + G11) / P3 + F11, 1)</f>
+        <v>8778.7999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2">
+        <v>355000</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4100</v>
+      </c>
+      <c r="G12" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="2">
+        <f>ROUND((E12 + G12) / P3 + F12, 1)</f>
+        <v>7908.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>17</v>
+      <c r="E13" s="2">
+        <v>420000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4400</v>
+      </c>
+      <c r="G13" s="2">
+        <v>13500</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="2">
+        <f>ROUND((E13 + G13) / P3 + F13, 1)</f>
+        <v>8778.7999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2">
+        <v>355000</v>
+      </c>
+      <c r="F14" s="2">
+        <v>4550</v>
+      </c>
+      <c r="G14" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="2">
+        <f>ROUND((E14 + G14) / P3 + F14, 1)</f>
+        <v>8358.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>17</v>
+      <c r="E15" s="2">
+        <v>420000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4650</v>
+      </c>
+      <c r="G15" s="2">
+        <v>13500</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="2">
+        <f>ROUND((E15 + G15) / P3 + F15, 1)</f>
+        <v>9028.7999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="2">
+        <v>355000</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4250</v>
+      </c>
+      <c r="G16" s="2">
+        <v>22000</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="2">
+        <f>ROUND((E16 + G16) / P3 + F16, 1)</f>
+        <v>8058.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>17</v>
+      <c r="E17" s="2">
+        <v>420000</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4420</v>
+      </c>
+      <c r="G17" s="2">
+        <v>13500</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="2">
+        <f>ROUND((E17 + G17) / P3 + F17, 1)</f>
+        <v>8798.7999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K18" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/calc_draft.xlsx
+++ b/calc_draft.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasus\Desktop\pythonapps\calculator_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9A7A19-D3D5-43D3-9EA5-716529724A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C302C745-9E88-4B5E-BBFE-9660ECCE6623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3285" windowWidth="23325" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="27">
   <si>
     <t>Country of discharge</t>
   </si>
@@ -93,9 +93,6 @@
     <t>container</t>
   </si>
   <si>
-    <t>validity</t>
-  </si>
-  <si>
     <t>railway(rub)</t>
   </si>
   <si>
@@ -112,16 +109,31 @@
   </si>
   <si>
     <t>total(usd)</t>
+  </si>
+  <si>
+    <t>validity from</t>
+  </si>
+  <si>
+    <t>validity till</t>
+  </si>
+  <si>
+    <t>30 nov</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -465,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -497,13 +509,13 @@
         <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -512,10 +524,13 @@
         <v>4</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -547,9 +562,12 @@
         <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="2">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="2">
         <f>ROUND((E2 + G2) / P3 + F2, 1)</f>
         <v>4543.3999999999996</v>
       </c>
@@ -583,14 +601,17 @@
         <v>9</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2">
+        <v>20</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="2">
         <f>ROUND((E3 + G3) / P3 + F3, 1)</f>
         <v>4455.6000000000004</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P3">
         <v>99</v>
@@ -625,9 +646,12 @@
         <v>9</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="2">
+        <v>20</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="2">
         <f>ROUND((E4 + G4) / P3 + F4, 1)</f>
         <v>4643.3999999999996</v>
       </c>
@@ -661,9 +685,12 @@
         <v>9</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="2">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="2">
         <f>ROUND((E5 + G5) / P3 + F5, 1)</f>
         <v>4555.6000000000004</v>
       </c>
@@ -697,9 +724,12 @@
         <v>9</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="2">
+        <v>20</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="2">
         <f>ROUND((E6 + G6) / P3 + F6, 1)</f>
         <v>4993.3999999999996</v>
       </c>
@@ -733,9 +763,12 @@
         <v>9</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="2">
+        <v>20</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="2">
         <f>ROUND((E7 + G7) / P3 + F7, 1)</f>
         <v>4805.6000000000004</v>
       </c>
@@ -769,9 +802,12 @@
         <v>9</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="2">
+        <v>20</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="2">
         <f>ROUND((E8 + G8) / P3 + F8, 1)</f>
         <v>4493.3999999999996</v>
       </c>
@@ -805,9 +841,12 @@
         <v>9</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="2">
+        <v>20</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="2">
         <f>ROUND((E9 + G9) / P3 + F9, 1)</f>
         <v>4505.6000000000004</v>
       </c>
@@ -841,9 +880,12 @@
         <v>9</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="2">
+        <v>20</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="2">
         <f>ROUND((E10 + G10) / P3 + F10, 1)</f>
         <v>8008.1</v>
       </c>
@@ -877,9 +919,12 @@
         <v>9</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="2">
+        <v>20</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="2">
         <f>ROUND((E11 + G11) / P3 + F11, 1)</f>
         <v>8778.7999999999993</v>
       </c>
@@ -913,9 +958,12 @@
         <v>9</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="2">
+        <v>20</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="2">
         <f>ROUND((E12 + G12) / P3 + F12, 1)</f>
         <v>7908.1</v>
       </c>
@@ -949,9 +997,12 @@
         <v>9</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="2">
+        <v>20</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="2">
         <f>ROUND((E13 + G13) / P3 + F13, 1)</f>
         <v>8778.7999999999993</v>
       </c>
@@ -985,9 +1036,12 @@
         <v>9</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="2">
+        <v>20</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="2">
         <f>ROUND((E14 + G14) / P3 + F14, 1)</f>
         <v>8358.1</v>
       </c>
@@ -1021,9 +1075,12 @@
         <v>9</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="2">
+        <v>20</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="2">
         <f>ROUND((E15 + G15) / P3 + F15, 1)</f>
         <v>9028.7999999999993</v>
       </c>
@@ -1057,14 +1114,17 @@
         <v>9</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="2">
+        <v>20</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="2">
         <f>ROUND((E16 + G16) / P3 + F16, 1)</f>
         <v>8058.1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -1093,18 +1153,19 @@
         <v>9</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="2">
+        <v>20</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="2">
         <f>ROUND((E17 + G17) / P3 + F17, 1)</f>
         <v>8798.7999999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K18" s="2"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:L17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>